--- a/inventory_export.xlsx
+++ b/inventory_export.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doe</t>
+          <t>argadfgdfgsdfgsdfg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgescu</t>
+          <t>Georgescuu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -637,6 +637,26 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aurelia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Abesei</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -707,7 +727,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -757,7 +777,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>LGGGGGGGGG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -767,7 +787,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -947,7 +967,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -977,7 +997,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -997,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,7 +1058,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>John argadfgdfgsdfgsdfg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1063,7 +1083,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>John argadfgdfgsdfgsdfg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1088,12 +1108,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>John argadfgdfgsdfgsdfg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monitor - LG</t>
+          <t>Monitor - LGGGGGGGGG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1227,6 +1247,81 @@
         </is>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>John argadfgdfgsdfgsdfg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Monitor - LGGGGGGGGG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>John argadfgdfgsdfgsdfg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Printer - Canon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>John argadfgdfgsdfgsdfg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Headset - Jabra</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
